--- a/Manuscript/Notation.xlsx
+++ b/Manuscript/Notation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hendersonhl/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hendersonhl/Documents/Articles/Poverty-Mapping/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D2AD92-FF79-4649-8A3A-4A52C8E15A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B691FCFF-E5F3-7F4F-955F-2E473E1A6A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="920" windowWidth="19900" windowHeight="19820" xr2:uid="{F1E70B07-EE08-EB48-82FB-87EAFBFB04A0}"/>
+    <workbookView xWindow="960" yWindow="760" windowWidth="19660" windowHeight="19880" xr2:uid="{F1E70B07-EE08-EB48-82FB-87EAFBFB04A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -493,13 +493,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,464 +845,464 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="A35" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="A36" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="A38" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="A41" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="A42" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="6" t="s">
         <v>87</v>
       </c>
     </row>

--- a/Manuscript/Notation.xlsx
+++ b/Manuscript/Notation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hendersonhl/Documents/Articles/Poverty-Mapping/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B691FCFF-E5F3-7F4F-955F-2E473E1A6A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749AB1D2-6F71-2B46-B569-762E22D8C969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="760" windowWidth="19660" windowHeight="19880" xr2:uid="{F1E70B07-EE08-EB48-82FB-87EAFBFB04A0}"/>
+    <workbookView xWindow="19680" yWindow="760" windowWidth="19660" windowHeight="19880" xr2:uid="{F1E70B07-EE08-EB48-82FB-87EAFBFB04A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="135">
   <si>
     <t>English</t>
   </si>
@@ -342,9 +342,6 @@
     <t>Intercept in R-squared model</t>
   </si>
   <si>
-    <t>Coefficient in R-squared model</t>
-  </si>
-  <si>
     <t>Error term in R-squared model</t>
   </si>
   <si>
@@ -411,9 +408,6 @@
     <t>delta</t>
   </si>
   <si>
-    <t>Coefficient in traditional SAE model</t>
-  </si>
-  <si>
     <t>q</t>
   </si>
   <si>
@@ -430,6 +424,24 @@
   </si>
   <si>
     <t>Error term in SAE model</t>
+  </si>
+  <si>
+    <t>Coefficient in area-level model</t>
+  </si>
+  <si>
+    <t>Error term in area-level model</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <t>Parameter in area-level model</t>
+  </si>
+  <si>
+    <t>Coefficient in model-assessment regression</t>
+  </si>
+  <si>
+    <t>zeta</t>
   </si>
 </sst>
 </file>
@@ -493,14 +505,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -815,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087A8632-CD5E-264F-B80A-2831C6B23145}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -823,17 +833,14 @@
     <col min="3" max="3" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>80</v>
       </c>
@@ -844,466 +851,488 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C29" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="6" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C39" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="6" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Manuscript/Notation.xlsx
+++ b/Manuscript/Notation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hendersonhl/Documents/Articles/Poverty-Mapping/Manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749AB1D2-6F71-2B46-B569-762E22D8C969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2317908-66DA-DD46-89A0-A35D28C897D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19680" yWindow="760" windowWidth="19660" windowHeight="19880" xr2:uid="{F1E70B07-EE08-EB48-82FB-87EAFBFB04A0}"/>
+    <workbookView xWindow="14900" yWindow="760" windowWidth="19660" windowHeight="19880" xr2:uid="{F1E70B07-EE08-EB48-82FB-87EAFBFB04A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="137">
   <si>
     <t>English</t>
   </si>
@@ -442,6 +442,12 @@
   </si>
   <si>
     <t>zeta</t>
+  </si>
+  <si>
+    <t>theta</t>
+  </si>
+  <si>
+    <t>Coefficient in unit-level model</t>
   </si>
 </sst>
 </file>
@@ -825,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087A8632-CD5E-264F-B80A-2831C6B23145}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1238,21 +1244,21 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
         <v>99</v>
@@ -1260,78 +1266,89 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>101</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>99</v>
       </c>
     </row>
